--- a/testcases/autotest_case1.xlsx
+++ b/testcases/autotest_case1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30240" windowHeight="13380"/>
+    <workbookView windowWidth="30240" windowHeight="13420"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
     <t>type</t>
   </si>
   <si>
-    <t xml:space="preserve">is_login_case </t>
+    <t>run_status</t>
   </si>
   <si>
     <t>expected_code</t>
